--- a/02_DIA_inicio_2026_analisis_assets/rbd_9416_escuela-poetas-de-chile_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9416_escuela-poetas-de-chile_nt2_rubricas.xlsx
@@ -1908,13 +1908,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2D6ACAF-FAC4-4968-9C95-97130888E728}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B45818E-ADBB-4F06-93FA-AF7EEE98B8EE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B683164-5A82-4833-8A29-0EF77A9E5FBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFDE1CBB-F4AD-4758-A85E-1DFFE3696CE3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50EE985B-F140-416F-9DA2-12962AF2B117}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A9D22A0-318E-4146-A3D7-0BE5CC2C7E9C}"/>
 </file>